--- a/system_development/Pintail/v0.1.3/BOM-Pintail_v0.1.3.xlsx
+++ b/system_development/Pintail/v0.1.3/BOM-Pintail_v0.1.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/austindowney/Documents/GitHub/FUSE-Head/system_development/Pintail/v0.1.3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacob Parker\Documents\GitHub\FUSE-Head\system_development\Pintail\v0.1.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ABC483-669C-1A40-B408-72F272A2C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD1515-F05E-4D9B-A0D6-0380C64CFB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="14620" windowHeight="9100" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294965908" uniqueCount="32">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -74,12 +74,6 @@
     <t>MFR / Vendor Description</t>
   </si>
   <si>
-    <t>Amount Per Cable</t>
-  </si>
-  <si>
-    <t>Total Cost (Per Cable)</t>
-  </si>
-  <si>
     <t>Primary or Alternative Part</t>
   </si>
   <si>
@@ -96,6 +90,48 @@
   </si>
   <si>
     <t>3D printer</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Base Plate</t>
+  </si>
+  <si>
+    <t>eBay/Thorlabs</t>
+  </si>
+  <si>
+    <t>https://ebay.io/m/f6G3qt</t>
+  </si>
+  <si>
+    <t>MB1530F/M</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/358877803352?_skw=Ender-3+V3+SE&amp;itmmeta=01M2TYF0HS0RC7X1RMY7WM5HW6&amp;hash=item538ec8b358:g:ddYAAOSwXoJnY9nE&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xA2EPZJQPcGE1EAq1tC18dEeFGkmdw%2FO3yULJCb%2FLgEIYOCE3MprIc5tdL%2BIOKs%2BUZ09USxeZvzKKTDMYC8HRTUEG2s73wZ6c2uZACigKpDz1AC0B9eT16UwF2jKtSmd4%2F3dPsAADyPIxcKus3D1nQFbdMHV%2BL6OvEO%2F%2BH0rKUtRlpy7TOHvso5eF1cIrnV4Ff21qKD4mrOmTSiVrft4rttj1kG2ouSakaqG7YIsw1D8D6p6wIbX%2FQVWkZP6tPh9uarYM6ylgndHiyrIbIOZjTWNA6JZlBZ7zKYJHhHLBb0sw%3D%3D%7Ctkp%3ABk9SR-KJvN6WaA</t>
+  </si>
+  <si>
+    <t>https://ebay.io/m/Pv82yd</t>
+  </si>
+  <si>
+    <t>eBay</t>
+  </si>
+  <si>
+    <t>Profilometer</t>
+  </si>
+  <si>
+    <t>optoNCDT 1420</t>
+  </si>
+  <si>
+    <t>https://ebay.io/m/m0SpLD</t>
+  </si>
+  <si>
+    <t>MICRO EPSILON CT-SF15-C3</t>
+  </si>
+  <si>
+    <t>Pyrometer</t>
   </si>
 </sst>
 </file>
@@ -188,7 +224,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -247,6 +283,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -585,29 +622,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="79" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.5" customWidth="1"/>
-    <col min="12" max="12" width="62.5" customWidth="1"/>
-    <col min="13" max="13" width="55.83203125" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.42578125" customWidth="1"/>
+    <col min="12" max="12" width="62.42578125" customWidth="1"/>
+    <col min="13" max="13" width="55.85546875" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>11</v>
@@ -616,13 +653,13 @@
         <v>9</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>8</v>
@@ -646,63 +683,127 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="9">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="G2" s="9">
-        <v>75</v>
+        <f>E2*F2</f>
+        <v>218</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="19">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>89</v>
+      </c>
+      <c r="G3" s="9">
+        <f>E3*F3</f>
+        <v>178</v>
+      </c>
       <c r="H3" s="5"/>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="17"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="19">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9">
+        <v>717.57</v>
+      </c>
+      <c r="G4" s="9">
+        <f>E4*F4</f>
+        <v>717.57</v>
+      </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="21"/>
+      <c r="I4" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="22">
+        <v>836</v>
+      </c>
+      <c r="G5" s="22">
+        <f>E5*F5</f>
+        <v>836</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17"/>
       <c r="C6" s="2"/>
       <c r="D6" s="20"/>
@@ -711,7 +812,7 @@
       <c r="G6" s="9"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="17"/>
       <c r="C7" s="2"/>
@@ -723,7 +824,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="17"/>
       <c r="C8" s="2"/>
@@ -735,7 +836,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="2"/>
@@ -747,7 +848,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="17"/>
       <c r="C10" s="2"/>
@@ -759,7 +860,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="17"/>
       <c r="C11" s="4"/>
@@ -771,7 +872,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="17"/>
       <c r="C12" s="2"/>
@@ -783,7 +884,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="17"/>
       <c r="C13" s="2"/>
@@ -795,7 +896,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="17"/>
       <c r="C14" s="2"/>
@@ -807,7 +908,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="17"/>
       <c r="C15" s="2"/>
@@ -818,7 +919,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="2"/>
@@ -830,7 +931,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="17"/>
       <c r="C17" s="2"/>
@@ -842,7 +943,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -855,7 +956,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -867,7 +968,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -878,25 +979,28 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G22" s="5">
         <f>SUM(G2:G21)</f>
-        <v>75</v>
+        <v>1949.5700000000002</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" tooltip="Original URL: https://store.creality.com/products/ender-3-v3-se-3d-printer?spm=..product_accf228c-979f-450e-90b4-4d88e008979f.0.1. Click or tap if you trust this link." display="https://nam02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fstore.creality.com%2Fproducts%2Fender-3-v3-se-3d-printer%3Fspm%3D..product_accf228c-979f-450e-90b4-4d88e008979f.0.1&amp;data=05%7C02%7CJHPARKER%40email.sc.edu%7Ca352611c2134487fcf1808df150dcc02%7C4b2a4b19d135420e8bb2b1cd238998cc%7C0%7C0%7C639252821129488256%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=VJaeAAT8rnG%2FPhk3%2Bme9G0Ml1MFBbcEWWrzPLMmHcYQ%3D&amp;reserved=0" xr:uid="{27A3E46D-50E1-4DC7-B0D5-E25881E90590}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{7ADE7E6E-21C8-4F58-ACA1-5A38A4D4B861}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{FE117B5E-B3DD-4FD5-8F6E-A2763073C8B4}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{172CEEC9-8580-4E74-BBB5-A0629D854C08}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/system_development/Pintail/v0.1.3/BOM-Pintail_v0.1.3.xlsx
+++ b/system_development/Pintail/v0.1.3/BOM-Pintail_v0.1.3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacob Parker\Documents\GitHub\FUSE-Head\system_development\Pintail\v0.1.3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ad8d35fc1f26fdcc/Documents/GitHub/FUSE-Head2/system_development/Pintail/v0.1.3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD1515-F05E-4D9B-A0D6-0380C64CFB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{F2BD1515-F05E-4D9B-A0D6-0380C64CFB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C2FD419-C946-4888-ACD8-6872553FB1E4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="14620" windowHeight="9100" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294965908" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -98,12 +98,6 @@
     <t>Total Cost</t>
   </si>
   <si>
-    <t>Base Plate</t>
-  </si>
-  <si>
-    <t>eBay/Thorlabs</t>
-  </si>
-  <si>
     <t>https://ebay.io/m/f6G3qt</t>
   </si>
   <si>
@@ -132,6 +126,18 @@
   </si>
   <si>
     <t>Pyrometer</t>
+  </si>
+  <si>
+    <t>Base Plate(200x100x12mm)</t>
+  </si>
+  <si>
+    <t>AliExpress</t>
+  </si>
+  <si>
+    <t>Base Plate(300x150x12.7mm)</t>
+  </si>
+  <si>
+    <t>eBay/Thorlabs/AliExpress</t>
   </si>
 </sst>
 </file>
@@ -178,11 +184,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -621,25 +629,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="27.44140625" customWidth="1"/>
+    <col min="3" max="3" width="37.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="79" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.42578125" customWidth="1"/>
-    <col min="12" max="12" width="62.42578125" customWidth="1"/>
-    <col min="13" max="13" width="55.85546875" customWidth="1"/>
+    <col min="10" max="10" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.44140625" customWidth="1"/>
+    <col min="12" max="12" width="62.44140625" customWidth="1"/>
+    <col min="13" max="13" width="55.88671875" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -683,7 +691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -711,109 +719,126 @@
         <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>20</v>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="C3" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="19">
         <v>2</v>
       </c>
       <c r="F3" s="9">
-        <v>89</v>
+        <v>39.590000000000003</v>
       </c>
       <c r="G3" s="9">
-        <f>E3*F3</f>
-        <v>178</v>
+        <v>79.180000000000007</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>26</v>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E4" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="9">
-        <v>717.57</v>
+        <v>89</v>
       </c>
       <c r="G4" s="9">
         <f>E4*F4</f>
-        <v>717.57</v>
+        <v>178</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="4"/>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="9">
+        <v>717.57</v>
+      </c>
+      <c r="G5" s="9">
+        <f>E5*F5</f>
+        <v>717.57</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="22">
         <v>836</v>
       </c>
-      <c r="G5" s="22">
-        <f>E5*F5</f>
+      <c r="G6" s="22">
+        <f>E6*F6</f>
         <v>836</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="17"/>
       <c r="C7" s="2"/>
       <c r="D7" s="20"/>
@@ -821,10 +846,9 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="17"/>
       <c r="C8" s="2"/>
@@ -836,9 +860,9 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="2"/>
       <c r="D9" s="20"/>
       <c r="E9" s="2"/>
@@ -848,9 +872,9 @@
       <c r="I9" s="1"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
-      <c r="B10" s="17"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="2"/>
       <c r="D10" s="20"/>
       <c r="E10" s="2"/>
@@ -860,10 +884,10 @@
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="17"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="20"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9"/>
@@ -872,11 +896,11 @@
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="17"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="16"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -884,11 +908,11 @@
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="17"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="20"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="2"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
@@ -896,11 +920,11 @@
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="17"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="16"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="2"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -908,55 +932,55 @@
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="17"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="20"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="5"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="2"/>
       <c r="D16" s="20"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="3"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="5"/>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13"/>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="8"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -965,42 +989,55 @@
       <c r="F19" s="13"/>
       <c r="G19" s="9"/>
       <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F22" s="7" t="s">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="5">
-        <f>SUM(G2:G21)</f>
-        <v>1949.5700000000002</v>
+      <c r="G23" s="5">
+        <f>SUM(G2:G22)</f>
+        <v>2028.75</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" tooltip="Original URL: https://store.creality.com/products/ender-3-v3-se-3d-printer?spm=..product_accf228c-979f-450e-90b4-4d88e008979f.0.1. Click or tap if you trust this link." display="https://nam02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fstore.creality.com%2Fproducts%2Fender-3-v3-se-3d-printer%3Fspm%3D..product_accf228c-979f-450e-90b4-4d88e008979f.0.1&amp;data=05%7C02%7CJHPARKER%40email.sc.edu%7Ca352611c2134487fcf1808df150dcc02%7C4b2a4b19d135420e8bb2b1cd238998cc%7C0%7C0%7C639252821129488256%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=VJaeAAT8rnG%2FPhk3%2Bme9G0Ml1MFBbcEWWrzPLMmHcYQ%3D&amp;reserved=0" xr:uid="{27A3E46D-50E1-4DC7-B0D5-E25881E90590}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{7ADE7E6E-21C8-4F58-ACA1-5A38A4D4B861}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{FE117B5E-B3DD-4FD5-8F6E-A2763073C8B4}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{172CEEC9-8580-4E74-BBB5-A0629D854C08}"/>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{7ADE7E6E-21C8-4F58-ACA1-5A38A4D4B861}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{FE117B5E-B3DD-4FD5-8F6E-A2763073C8B4}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{172CEEC9-8580-4E74-BBB5-A0629D854C08}"/>
+    <hyperlink ref="I2" r:id="rId4" tooltip="Original URL: https://store.creality.com/products/ender-3-v3-se-3d-printer?spm=..product_accf228c-979f-450e-90b4-4d88e008979f.0.1. Click or tap if you trust this link." display="https://nam02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fstore.creality.com%2Fproducts%2Fender-3-v3-se-3d-printer%3Fspm%3D..product_accf228c-979f-450e-90b4-4d88e008979f.0.1&amp;data=05%7C02%7CJHPARKER%40email.sc.edu%7Ca352611c2134487fcf1808df150dcc02%7C4b2a4b19d135420e8bb2b1cd238998cc%7C0%7C0%7C639252821129488256%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=VJaeAAT8rnG%2FPhk3%2Bme9G0Ml1MFBbcEWWrzPLMmHcYQ%3D&amp;reserved=0" xr:uid="{27A3E46D-50E1-4DC7-B0D5-E25881E90590}"/>
+    <hyperlink ref="J4" r:id="rId5" xr:uid="{B6ED6A72-4FD5-4E4F-BA83-5D6C407C86D7}"/>
+    <hyperlink ref="I3" r:id="rId6" xr:uid="{95DA01EE-1CC0-42ED-B4EC-777EB3334406}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>